--- a/LineTapes+Recordings.xlsx
+++ b/LineTapes+Recordings.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\01_LIFE\01_Projects\01-EGC-Website\ennisgc.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E7EDF5D4-48E8-49D1-9A01-9C494E840953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF96F6C-1930-4CA8-950C-A9DE1A8994F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="0" windowWidth="29040" windowHeight="15840" xr2:uid="{56BE2339-60D8-4A18-AABB-AD9E485896A0}"/>
+    <workbookView xWindow="5880" yWindow="0" windowWidth="22920" windowHeight="15600" xr2:uid="{56BE2339-60D8-4A18-AABB-AD9E485896A0}"/>
   </bookViews>
   <sheets>
     <sheet name="LineTapes+Recordings" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LineTapes+Recordings'!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
   <si>
     <t>Alto LTs</t>
   </si>
@@ -221,6 +224,129 @@
   </si>
   <si>
     <t>BT-drift-away.mp3</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Christmas</t>
+  </si>
+  <si>
+    <t>General</t>
+  </si>
+  <si>
+    <t>Gospel</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>O Holy Night</t>
+  </si>
+  <si>
+    <t>Silent Night</t>
+  </si>
+  <si>
+    <t>War is Over</t>
+  </si>
+  <si>
+    <t>Winter Wonderland</t>
+  </si>
+  <si>
+    <t>Chain Reaction</t>
+  </si>
+  <si>
+    <t>Ho Hey</t>
+  </si>
+  <si>
+    <t>Lovely Day</t>
+  </si>
+  <si>
+    <t>Aint No Mountain High Enough</t>
+  </si>
+  <si>
+    <t>Drift Away</t>
+  </si>
+  <si>
+    <t>Money Money Money</t>
+  </si>
+  <si>
+    <t>No Place Id Rather Be</t>
+  </si>
+  <si>
+    <t>Something Inside So Strong</t>
+  </si>
+  <si>
+    <t>Jesus Promised</t>
+  </si>
+  <si>
+    <t>No Ways Tired</t>
+  </si>
+  <si>
+    <t>Strong Hold</t>
+  </si>
+  <si>
+    <t>Roar</t>
+  </si>
+  <si>
+    <t>My Life if in Your Hands</t>
+  </si>
+  <si>
+    <t>Put a Little Love in Your Heart</t>
+  </si>
+  <si>
+    <t>BT-blitzen.mp3</t>
+  </si>
+  <si>
+    <t>BT-Have-Yourself-A-Merry-Little-Christmas.mp3</t>
+  </si>
+  <si>
+    <t>Have Yourself a Merry Little Christmas</t>
+  </si>
+  <si>
+    <t>BT-I-Wish-It-Could-Be-Christmas-Everyday.m4a</t>
+  </si>
+  <si>
+    <t>I Wish it Could be Christmas Everyday</t>
+  </si>
+  <si>
+    <t>BT-jingle-bells.mp3</t>
+  </si>
+  <si>
+    <t>Jingle Bells</t>
+  </si>
+  <si>
+    <t>BT-O-Come-All-Ye-Faithful.mp3</t>
+  </si>
+  <si>
+    <t>O Come All Ye Faithful</t>
+  </si>
+  <si>
+    <t>Rudolf the Red Nosed Reindeer</t>
+  </si>
+  <si>
+    <t>BT-Winter-Wonderland</t>
+  </si>
+  <si>
+    <t>Page</t>
+  </si>
+  <si>
+    <t>Index Page</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Extras</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>BT-Rudolph-the-Red-nosed-Reindeer.mp3</t>
+  </si>
+  <si>
+    <t>Blitzen's Boogie</t>
   </si>
 </sst>
 </file>
@@ -1088,264 +1214,585 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD2CC447-AA4F-42FD-92AE-E5162B5F5C32}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="40.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="33" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E1" t="s">
         <v>59</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="L1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>28</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="H8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" t="s">
+        <v>73</v>
+      </c>
+      <c r="C9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D9" t="s">
+        <v>103</v>
+      </c>
+      <c r="E9" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E10" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="F15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>103</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>103</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B18" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+      <c r="D18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>103</v>
+      </c>
+      <c r="D19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D20" t="s">
+        <v>103</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" t="s">
+        <v>84</v>
+      </c>
+      <c r="F21" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G21" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H21" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="F22" t="s">
         <v>20</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G22" t="s">
         <v>21</v>
       </c>
-      <c r="D6" t="s">
+      <c r="H22" t="s">
         <v>22</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J22" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G23" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
+      <c r="H23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
+      <c r="G24" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
+      <c r="H24" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" t="s">
         <v>37</v>
       </c>
-      <c r="C12" t="s">
+      <c r="G25" t="s">
         <v>38</v>
       </c>
-      <c r="D12" t="s">
+      <c r="H25" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E17" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="G22" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K26" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{AD2CC447-AA4F-42FD-92AE-E5162B5F5C32}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
+      <sortCondition ref="A1"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>

--- a/LineTapes+Recordings.xlsx
+++ b/LineTapes+Recordings.xlsx
@@ -678,7 +678,7 @@
       <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
@@ -695,7 +695,7 @@
       <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -712,7 +712,7 @@
       <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -729,7 +729,7 @@
       <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -746,7 +746,7 @@
       <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
     </row>
@@ -766,13 +766,13 @@
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="2" t="s">
         <v>28</v>
       </c>
     </row>
@@ -789,10 +789,10 @@
       <c r="D8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -812,13 +812,13 @@
       <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="2" t="s">
         <v>35</v>
       </c>
     </row>
@@ -838,13 +838,13 @@
       <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="2" t="s">
         <v>39</v>
       </c>
     </row>
@@ -861,16 +861,16 @@
       <c r="D11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="2" t="s">
         <v>44</v>
       </c>
     </row>

--- a/LineTapes+Recordings.xlsx
+++ b/LineTapes+Recordings.xlsx
@@ -994,7 +994,7 @@
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
       <c r="H16" s="1" t="s">

--- a/LineTapes+Recordings.xlsx
+++ b/LineTapes+Recordings.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="108">
   <si>
     <t>Genre</t>
   </si>
@@ -68,6 +68,9 @@
     <t>BT-blitzen.mp3</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Have Yourself a Merry Little Christmas</t>
   </si>
   <si>
@@ -95,9 +98,6 @@
     <t>O Holy Night</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>LT-Alto-O-Holy-Night.mp3</t>
   </si>
   <si>
@@ -329,7 +329,7 @@
     <t>LT-Soprano-Put-a-Little-Love-in-Your-Heart.mp3</t>
   </si>
   <si>
-    <t>Strong Hold</t>
+    <t>Stronghold</t>
   </si>
   <si>
     <t>LT-Alto-Strong-Hold.mp3</t>
@@ -348,7 +348,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -359,6 +359,10 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -392,13 +396,16 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -681,13 +688,22 @@
       <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>14</v>
@@ -696,7 +712,16 @@
         <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="4">
@@ -704,7 +729,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>14</v>
@@ -713,7 +738,16 @@
         <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="5">
@@ -721,7 +755,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>14</v>
@@ -730,7 +764,16 @@
         <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -738,7 +781,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>14</v>
@@ -747,7 +790,16 @@
         <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -755,7 +807,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>14</v>
@@ -764,7 +816,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>26</v>
@@ -810,7 +862,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>33</v>
@@ -836,7 +888,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>37</v>
@@ -887,13 +939,22 @@
       <c r="D12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="4" t="s">
         <v>49</v>
       </c>
     </row>
@@ -910,25 +971,25 @@
       <c r="D13" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="H13" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -945,13 +1006,22 @@
       <c r="D14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="4" t="s">
         <v>61</v>
       </c>
     </row>
@@ -968,16 +1038,22 @@
       <c r="D15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="E15" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -994,10 +1070,16 @@
       <c r="D16" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="E16" s="3" t="s">
+        <v>16</v>
+      </c>
       <c r="F16" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="G16" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1014,7 +1096,19 @@
       <c r="D17" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1031,10 +1125,19 @@
       <c r="D18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="E18" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1051,13 +1154,22 @@
       <c r="D19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="E19" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K19" s="4" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1074,19 +1186,28 @@
       <c r="D20" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E20" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="J20" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="K20" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="L20" s="4" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1097,13 +1218,22 @@
       <c r="B21" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="C21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="2" t="s">
         <v>89</v>
       </c>
     </row>
@@ -1114,13 +1244,22 @@
       <c r="B22" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="C22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="2" t="s">
         <v>93</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -1134,13 +1273,22 @@
       <c r="B23" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="C23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="2" t="s">
         <v>98</v>
       </c>
     </row>
@@ -1151,13 +1299,22 @@
       <c r="B24" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="C24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="2" t="s">
         <v>102</v>
       </c>
     </row>
@@ -1165,16 +1322,25 @@
       <c r="A25" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="2" t="s">
         <v>106</v>
       </c>
     </row>

--- a/LineTapes+Recordings.xlsx
+++ b/LineTapes+Recordings.xlsx
@@ -1262,7 +1262,7 @@
       <c r="H22" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="J22" s="2" t="s">
         <v>94</v>
       </c>
     </row>
